--- a/data/2026/23-ialomita/92658-slobozia/budget_file.xlsx
+++ b/data/2026/23-ialomita/92658-slobozia/budget_file.xlsx
@@ -716,7 +716,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>03.02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Impozit pe venit</t>
         </is>
@@ -727,7 +732,11 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="n">
         <v>1100</v>
       </c>
@@ -760,7 +769,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>04.02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cote si sume defalcate din impozitul pe venit</t>
         </is>
@@ -771,7 +785,11 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="n">
         <v>78241</v>
       </c>
@@ -857,7 +875,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>07.02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Impozite si taxe pe proprietate</t>
         </is>
@@ -868,7 +891,11 @@
       <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n">
         <v>27850</v>
       </c>
@@ -1092,24 +1119,39 @@
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Sume defalcate din TVA (se scad)</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" s="3" t="n">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>35729</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>11.02 total: parent 35.729,00 != sum(children) 43.469,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1222,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Taxe pe servicii specifice</t>
         </is>
@@ -1191,7 +1238,11 @@
       <c r="E29" t="n">
         <v>1</v>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="n">
         <v>40</v>
       </c>
@@ -1224,7 +1275,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Taxe pe utilizarea bunurilor, autorizarea utilizarii bunurilor sau pe desfasurarea de activitati</t>
         </is>
@@ -1235,7 +1291,11 @@
       <c r="E31" t="n">
         <v>1</v>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="n">
         <v>7700</v>
       </c>
@@ -2286,7 +2346,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>43.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Subventii de la alte administratii</t>
         </is>
@@ -2297,7 +2362,11 @@
       <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="n">
         <v>16840.81</v>
       </c>
@@ -2418,7 +2487,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>45.02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Sume FEN postaderare in contul platilor efectuate</t>
         </is>
@@ -2429,7 +2503,11 @@
       <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G30" s="3" t="n">
         <v>136179.56</v>
       </c>
@@ -3077,7 +3155,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>50.02</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Partea I-a SERVICII PUBLICE GENERALE</t>
         </is>
@@ -3088,7 +3171,11 @@
       <c r="E53" t="n">
         <v>3</v>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="n">
         <v>28959.52</v>
       </c>
@@ -3099,24 +3186,39 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="2" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" s="3" t="n">
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
         <v>20766.72</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>51.02 total: parent 20.766,72 != sum(children) 618,10 (1 children)</t>
         </is>
       </c>
     </row>
@@ -3158,187 +3260,182 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" t="n">
         <v>106</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" t="n">
         <v>4</v>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="3" t="n">
         <v>15358</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" t="n">
         <v>107</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="3" t="n">
         <v>4755.62</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" t="n">
         <v>108</v>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" t="n">
         <v>109</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" t="n">
         <v>4</v>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="3" t="n">
         <v>618.1</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" t="n">
         <v>110</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="3" t="n">
         <v>618.1</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3484,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Alte servicii publice generale</t>
         </is>
@@ -3398,7 +3500,11 @@
       <c r="E63" t="n">
         <v>4</v>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G63" s="3" t="n">
         <v>3512.8</v>
       </c>
@@ -3446,76 +3552,74 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" t="n">
         <v>115</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" t="n">
         <v>4</v>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="3" t="n">
         <v>1910.8</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" t="n">
         <v>116</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="3" t="n">
         <v>602</v>
       </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -3523,6 +3627,11 @@
       <c r="A67" t="inlineStr">
         <is>
           <t>50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>54.02</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3595,7 +3704,12 @@
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>55.02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
@@ -3606,7 +3720,11 @@
       <c r="E70" t="n">
         <v>4</v>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G70" s="3" t="n">
         <v>4680</v>
       </c>
@@ -3654,39 +3772,38 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>55.02</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" t="n">
         <v>122</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -3694,6 +3811,11 @@
       <c r="A73" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>55.02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3744,7 +3866,12 @@
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="2" t="inlineStr">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>Partea a II-a APARARE, ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
@@ -3755,7 +3882,11 @@
       <c r="E75" t="n">
         <v>4</v>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G75" s="3" t="n">
         <v>8142.9</v>
       </c>
@@ -3766,7 +3897,12 @@
       </c>
     </row>
     <row r="76">
-      <c r="C76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>Ordine publica si siguranta nationala</t>
         </is>
@@ -3777,7 +3913,11 @@
       <c r="E76" t="n">
         <v>4</v>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G76" s="3" t="n">
         <v>8142.9</v>
       </c>
@@ -3825,76 +3965,74 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" t="n">
         <v>128</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" t="n">
         <v>4</v>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="3" t="n">
         <v>62.3</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>TITLUL VI TRANSFERURI INTRE UNITATI ALE ADMINISTRATIEI PUBLICE</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" t="n">
         <v>129</v>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" t="n">
         <v>4</v>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="3" t="n">
         <v>8080.6</v>
       </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -3965,7 +4103,12 @@
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>64.02</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
         <is>
           <t>Partea a III-a CHELTUIELI SOCIAL-CULTURALE</t>
         </is>
@@ -3976,7 +4119,11 @@
       <c r="E83" t="n">
         <v>4</v>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G83" s="3" t="n">
         <v>221053.67</v>
       </c>
@@ -3987,24 +4134,39 @@
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="2" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Invatamant</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" s="3" t="n">
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
         <v>140454.18</v>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>65.02 total: parent 140.454,18 != sum(children) 4.509,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -4046,76 +4208,74 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" t="n">
         <v>136</v>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" t="n">
         <v>4</v>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="3" t="n">
         <v>467.96</v>
       </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" t="n">
         <v>137</v>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" t="n">
         <v>4</v>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="3" t="n">
         <v>19703.04</v>
       </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -4125,6 +4285,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>TITLUL VII ALTE TRANSFERURI</t>
@@ -4151,298 +4316,290 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>Titlul VIII PROIECTE CU FINANTARE DIN FONDURI EXTERNE NERAMBURSABILE (FEN) POSTADERARE</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" t="n">
         <v>139</v>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="E89" t="n">
         <v>4</v>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="3" t="n">
         <v>92355.53999999999</v>
       </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>TITLUL IX ASISTENTA SOCIALA</t>
         </is>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" t="n">
         <v>140</v>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" t="n">
         <v>4</v>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="3" t="n">
         <v>2384.09</v>
       </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" t="n">
         <v>141</v>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" t="n">
         <v>4</v>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>TITLUL XII PROIECTE CU FINANTARE DIN SUMELE REPREZENTAND ASISTENTA FINANCIARA NERAMBURSABILA AFERENTA PNRR</t>
         </is>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" t="n">
         <v>142</v>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" t="n">
         <v>4</v>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="3" t="n">
         <v>20739.65</v>
       </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" t="n">
         <v>143</v>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" t="n">
         <v>4</v>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="G93" s="3" t="n">
         <v>3674</v>
       </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" t="n">
         <v>144</v>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" t="n">
         <v>4</v>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="G94" s="3" t="n">
         <v>3674</v>
       </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>OPERATIUNI FINANCIARE</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" t="n">
         <v>145</v>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="E95" t="n">
         <v>4</v>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="G95" s="3" t="n">
         <v>835</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>TITLUL XIX RAMBURSARI DE CREDITE</t>
         </is>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" t="n">
         <v>146</v>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" t="n">
         <v>5</v>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G96" s="3" t="n">
         <v>835</v>
       </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -4667,24 +4824,39 @@
       </c>
     </row>
     <row r="107">
-      <c r="C107" s="2" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Sanatate</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" s="3" t="n">
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n">
         <v>4138.5</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>66.02 total: parent 4.138,50 != sum(children) 4,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -4726,187 +4898,182 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" t="n">
         <v>159</v>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" t="n">
         <v>5</v>
       </c>
-      <c r="F109" s="6" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="3" t="n">
         <v>4015</v>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" t="n">
         <v>160</v>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" t="n">
         <v>5</v>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>TITLUL IV SUBVENTII</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" t="n">
         <v>161</v>
       </c>
-      <c r="E111" s="6" t="n">
+      <c r="E111" t="n">
         <v>5</v>
       </c>
-      <c r="F111" s="6" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="G111" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" t="n">
         <v>162</v>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" t="n">
         <v>5</v>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="G112" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" t="n">
         <v>163</v>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" t="n">
         <v>5</v>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="G113" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -4977,24 +5144,39 @@
       </c>
     </row>
     <row r="117">
-      <c r="C117" s="2" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Cultura, recreere si religie</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" s="3" t="n">
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="n">
         <v>41100.99</v>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>67.02 total: parent 41.100,99 != sum(children) 4.067,74 (1 children)</t>
         </is>
       </c>
     </row>
@@ -5036,261 +5218,254 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B119" s="6" t="n"/>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" t="n">
         <v>169</v>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" t="n">
         <v>5</v>
       </c>
-      <c r="F119" s="6" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
+      <c r="G119" s="3" t="n">
         <v>5805</v>
       </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" t="n">
         <v>170</v>
       </c>
-      <c r="E120" s="6" t="n">
+      <c r="E120" t="n">
         <v>5</v>
       </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G120" s="3" t="n">
         <v>6226</v>
       </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>TITLUL VI TRANSFERURI INTRE UNITATI ALE ADMINISTRATIEI PUBLICE</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" t="n">
         <v>171</v>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" t="n">
         <v>5</v>
       </c>
-      <c r="F121" s="6" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="3" t="n">
         <v>23264.1</v>
       </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" t="n">
         <v>172</v>
       </c>
-      <c r="E122" s="6" t="n">
+      <c r="E122" t="n">
         <v>5</v>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
+      <c r="G122" s="3" t="n">
         <v>186.16</v>
       </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B123" s="6" t="n"/>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>TITLUL XII PROIECTE CU FINANTARE DIN SUMELE REPREZENTAND ASISTENTA FINANCIARA NERAMBURSABILA AFERENTA PNRR</t>
         </is>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" t="n">
         <v>173</v>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" t="n">
         <v>5</v>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="3" t="n">
         <v>1551.98</v>
       </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" t="n">
         <v>174</v>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" t="n">
         <v>5</v>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G124" s="3" t="n">
         <v>4067.74</v>
       </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" t="n">
         <v>175</v>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" t="n">
         <v>5</v>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
+      <c r="G125" s="3" t="n">
         <v>4067.74</v>
       </c>
-      <c r="H125" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -5405,24 +5580,39 @@
       </c>
     </row>
     <row r="131">
-      <c r="C131" s="2" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" s="3" t="n">
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="n">
         <v>35360</v>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>68.02 total: parent 35.360,00 != sum(children) 235,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -5464,187 +5654,182 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" t="n">
         <v>183</v>
       </c>
-      <c r="E133" s="6" t="n">
+      <c r="E133" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G133" s="3" t="n">
         <v>15118</v>
       </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" t="n">
         <v>184</v>
       </c>
-      <c r="E134" s="6" t="n">
+      <c r="E134" t="n">
         <v>5</v>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
+      <c r="G134" s="3" t="n">
         <v>2915</v>
       </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>TITLUL IX ASISTENTA SOCIALA</t>
         </is>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" t="n">
         <v>185</v>
       </c>
-      <c r="E135" s="6" t="n">
+      <c r="E135" t="n">
         <v>5</v>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="3" t="n">
         <v>17092</v>
       </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" t="n">
         <v>186</v>
       </c>
-      <c r="E136" s="6" t="n">
+      <c r="E136" t="n">
         <v>5</v>
       </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
+      <c r="G136" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B137" s="6" t="n"/>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" t="n">
         <v>187</v>
       </c>
-      <c r="E137" s="6" t="n">
+      <c r="E137" t="n">
         <v>6</v>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -5847,7 +6032,12 @@
       </c>
     </row>
     <row r="147">
-      <c r="C147" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>69.02</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Partea a IV-a SERVICII SI DEZVOLTARE PUBLICA, LOCUINTE, MEDIU SI APE</t>
         </is>
@@ -5858,7 +6048,11 @@
       <c r="E147" t="n">
         <v>6</v>
       </c>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G147" s="3" t="n">
         <v>65055.14</v>
       </c>
@@ -5869,24 +6063,39 @@
       </c>
     </row>
     <row r="148">
-      <c r="C148" s="2" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" s="3" t="n">
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="n">
         <v>37993.48</v>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>70.02 total: parent 37.993,48 != sum(children) 10.111,20 (2 children)</t>
         </is>
       </c>
     </row>
@@ -5928,113 +6137,110 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="6" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D150" t="n">
         <v>200</v>
       </c>
-      <c r="E150" s="6" t="n">
+      <c r="E150" t="n">
         <v>6</v>
       </c>
-      <c r="F150" s="6" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
+      <c r="G150" s="3" t="n">
         <v>403.23</v>
       </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" t="n">
         <v>201</v>
       </c>
-      <c r="E151" s="6" t="n">
+      <c r="E151" t="n">
         <v>6</v>
       </c>
-      <c r="F151" s="6" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
+      <c r="G151" s="3" t="n">
         <v>7195</v>
       </c>
-      <c r="H151" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>Titlul VIII PROIECTE CU FINANTARE DIN FONDURI EXTERNE NERAMBURSABILE (FEN) POSTADERARE</t>
         </is>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" t="n">
         <v>202</v>
       </c>
-      <c r="E152" s="6" t="n">
+      <c r="E152" t="n">
         <v>6</v>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
+      <c r="G152" s="3" t="n">
         <v>3210</v>
       </c>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -6044,6 +6250,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
           <t>TITLUL X Proiecte cu finantare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020</t>
@@ -6070,187 +6281,182 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="6" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D154" s="6" t="n">
+      <c r="D154" t="n">
         <v>204</v>
       </c>
-      <c r="E154" s="6" t="n">
+      <c r="E154" t="n">
         <v>6</v>
       </c>
-      <c r="F154" s="6" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
+      <c r="G154" s="3" t="n">
         <v>9.56</v>
       </c>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="6" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="inlineStr">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" t="n">
         <v>205</v>
       </c>
-      <c r="E155" s="6" t="n">
+      <c r="E155" t="n">
         <v>6</v>
       </c>
-      <c r="F155" s="6" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
+      <c r="G155" s="3" t="n">
         <v>9306.84</v>
       </c>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B156" s="6" t="n"/>
-      <c r="C156" s="6" t="inlineStr">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D156" s="6" t="n">
+      <c r="D156" t="n">
         <v>206</v>
       </c>
-      <c r="E156" s="6" t="n">
+      <c r="E156" t="n">
         <v>6</v>
       </c>
-      <c r="F156" s="6" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
+      <c r="G156" s="3" t="n">
         <v>9306.84</v>
       </c>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="6" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>OPERATIUNI FINANCIARE</t>
         </is>
       </c>
-      <c r="D157" s="6" t="n">
+      <c r="D157" t="n">
         <v>207</v>
       </c>
-      <c r="E157" s="6" t="n">
+      <c r="E157" t="n">
         <v>6</v>
       </c>
-      <c r="F157" s="6" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
+      <c r="G157" s="3" t="n">
         <v>804.36</v>
       </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>TITLUL XIX RAMBURSARI DE CREDITE</t>
         </is>
       </c>
-      <c r="D158" s="6" t="n">
+      <c r="D158" t="n">
         <v>208</v>
       </c>
-      <c r="E158" s="6" t="n">
+      <c r="E158" t="n">
         <v>6</v>
       </c>
-      <c r="F158" s="6" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
+      <c r="G158" s="3" t="n">
         <v>804.36</v>
       </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -6343,24 +6549,39 @@
       </c>
     </row>
     <row r="163">
-      <c r="C163" s="2" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>Protectia mediului</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" s="3" t="n">
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="n">
         <v>27061.66</v>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>74.02 total: parent 27.061,66 != sum(children) 8.241,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -6402,298 +6623,290 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B165" s="6" t="n"/>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D165" t="n">
         <v>215</v>
       </c>
-      <c r="E165" s="6" t="n">
+      <c r="E165" t="n">
         <v>6</v>
       </c>
-      <c r="F165" s="6" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
+      <c r="G165" s="3" t="n">
         <v>2772.38</v>
       </c>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D166" s="6" t="n">
+      <c r="D166" t="n">
         <v>216</v>
       </c>
-      <c r="E166" s="6" t="n">
+      <c r="E166" t="n">
         <v>6</v>
       </c>
-      <c r="F166" s="6" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
+      <c r="G166" s="3" t="n">
         <v>2185.79</v>
       </c>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B167" s="6" t="n"/>
-      <c r="C167" s="6" t="inlineStr">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D167" s="6" t="n">
+      <c r="D167" t="n">
         <v>217</v>
       </c>
-      <c r="E167" s="6" t="n">
+      <c r="E167" t="n">
         <v>6</v>
       </c>
-      <c r="F167" s="6" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
+      <c r="G167" s="3" t="n">
         <v>77.42</v>
       </c>
-      <c r="H167" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B168" s="6" t="n"/>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>TITLUL XII PROIECTE CU FINANTARE DIN SUMELE REPREZENTAND ASISTENTA FINANCIARA NERAMBURSABILA AFERENTA PNRR</t>
         </is>
       </c>
-      <c r="D168" s="6" t="n">
+      <c r="D168" t="n">
         <v>218</v>
       </c>
-      <c r="E168" s="6" t="n">
+      <c r="E168" t="n">
         <v>6</v>
       </c>
-      <c r="F168" s="6" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
+      <c r="G168" s="3" t="n">
         <v>13784.58</v>
       </c>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="inlineStr">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D169" s="6" t="n">
+      <c r="D169" t="n">
         <v>219</v>
       </c>
-      <c r="E169" s="6" t="n">
+      <c r="E169" t="n">
         <v>6</v>
       </c>
-      <c r="F169" s="6" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
+      <c r="G169" s="3" t="n">
         <v>5741.5</v>
       </c>
-      <c r="H169" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="6" t="inlineStr">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D170" s="6" t="n">
+      <c r="D170" t="n">
         <v>220</v>
       </c>
-      <c r="E170" s="6" t="n">
+      <c r="E170" t="n">
         <v>6</v>
       </c>
-      <c r="F170" s="6" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
+      <c r="G170" s="3" t="n">
         <v>5741.5</v>
       </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="inlineStr">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
         <is>
           <t>OPERATIUNI FINANCIARE</t>
         </is>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D171" t="n">
         <v>221</v>
       </c>
-      <c r="E171" s="6" t="n">
+      <c r="E171" t="n">
         <v>6</v>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
+      <c r="G171" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="inlineStr">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
         <is>
           <t>TITLUL XIX RAMBURSARI DE CREDITE</t>
         </is>
       </c>
-      <c r="D172" s="6" t="n">
+      <c r="D172" t="n">
         <v>222</v>
       </c>
-      <c r="E172" s="6" t="n">
+      <c r="E172" t="n">
         <v>6</v>
       </c>
-      <c r="F172" s="6" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
+      <c r="G172" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6999,12 @@
       </c>
     </row>
     <row r="177">
-      <c r="C177" s="2" t="inlineStr">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>79.02</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>Partea a V-a ACTIUNI ECONOMICE</t>
         </is>
@@ -6797,7 +7015,11 @@
       <c r="E177" t="n">
         <v>6</v>
       </c>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G177" s="3" t="n">
         <v>55998.28</v>
       </c>
@@ -6808,24 +7030,39 @@
       </c>
     </row>
     <row r="178">
-      <c r="C178" s="2" t="inlineStr">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>Transporturi</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" s="3" t="n">
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
         <v>54798.28</v>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>84.02 total: parent 54.798,28 != sum(children) 21.256,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -6867,372 +7104,362 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B180" s="6" t="n"/>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D180" s="6" t="n">
+      <c r="D180" t="n">
         <v>230</v>
       </c>
-      <c r="E180" s="6" t="n">
+      <c r="E180" t="n">
         <v>7</v>
       </c>
-      <c r="F180" s="6" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
+      <c r="G180" s="3" t="n">
         <v>3885.77</v>
       </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B181" s="6" t="n"/>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D181" s="6" t="n">
+      <c r="D181" t="n">
         <v>231</v>
       </c>
-      <c r="E181" s="6" t="n">
+      <c r="E181" t="n">
         <v>7</v>
       </c>
-      <c r="F181" s="6" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
+      <c r="G181" s="3" t="n">
         <v>4348.15</v>
       </c>
-      <c r="H181" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="6" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
         <is>
           <t>TITLUL IV SUBVENTII</t>
         </is>
       </c>
-      <c r="D182" s="6" t="n">
+      <c r="D182" t="n">
         <v>232</v>
       </c>
-      <c r="E182" s="6" t="n">
+      <c r="E182" t="n">
         <v>7</v>
       </c>
-      <c r="F182" s="6" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
+      <c r="G182" s="3" t="n">
         <v>5880</v>
       </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
         <is>
           <t>Titlul VIII PROIECTE CU FINANTARE DIN FONDURI EXTERNE NERAMBURSABILE (FEN) POSTADERARE</t>
         </is>
       </c>
-      <c r="D183" s="6" t="n">
+      <c r="D183" t="n">
         <v>233</v>
       </c>
-      <c r="E183" s="6" t="n">
+      <c r="E183" t="n">
         <v>7</v>
       </c>
-      <c r="F183" s="6" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
+      <c r="G183" s="3" t="n">
         <v>15506.5</v>
       </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="6" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="inlineStr">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
         <is>
           <t>TITLUL XI ALTE CHELTUIELI</t>
         </is>
       </c>
-      <c r="D184" s="6" t="n">
+      <c r="D184" t="n">
         <v>234</v>
       </c>
-      <c r="E184" s="6" t="n">
+      <c r="E184" t="n">
         <v>7</v>
       </c>
-      <c r="F184" s="6" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
+      <c r="G184" s="3" t="n">
         <v>84.45</v>
       </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
         <is>
           <t>TITLUL XII PROIECTE CU FINANTARE DIN SUMELE REPREZENTAND ASISTENTA FINANCIARA NERAMBURSABILA AFERENTA PNRR</t>
         </is>
       </c>
-      <c r="D185" s="6" t="n">
+      <c r="D185" t="n">
         <v>235</v>
       </c>
-      <c r="E185" s="6" t="n">
+      <c r="E185" t="n">
         <v>7</v>
       </c>
-      <c r="F185" s="6" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
+      <c r="G185" s="3" t="n">
         <v>3837.42</v>
       </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B186" s="6" t="n"/>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D186" s="6" t="n">
+      <c r="D186" t="n">
         <v>236</v>
       </c>
-      <c r="E186" s="6" t="n">
+      <c r="E186" t="n">
         <v>7</v>
       </c>
-      <c r="F186" s="6" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
+      <c r="G186" s="3" t="n">
         <v>17580</v>
       </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I186" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D187" s="6" t="n">
+      <c r="D187" t="n">
         <v>237</v>
       </c>
-      <c r="E187" s="6" t="n">
+      <c r="E187" t="n">
         <v>7</v>
       </c>
-      <c r="F187" s="6" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
+      <c r="G187" s="3" t="n">
         <v>17580</v>
       </c>
-      <c r="H187" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="6" t="inlineStr">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>OPERATIUNI FINANCIARE</t>
         </is>
       </c>
-      <c r="D188" s="6" t="n">
+      <c r="D188" t="n">
         <v>238</v>
       </c>
-      <c r="E188" s="6" t="n">
+      <c r="E188" t="n">
         <v>7</v>
       </c>
-      <c r="F188" s="6" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
+      <c r="G188" s="3" t="n">
         <v>3676</v>
       </c>
-      <c r="H188" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I188" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>TITLUL XIX RAMBURSARI DE CREDITE</t>
         </is>
       </c>
-      <c r="D189" s="6" t="n">
+      <c r="D189" t="n">
         <v>239</v>
       </c>
-      <c r="E189" s="6" t="n">
+      <c r="E189" t="n">
         <v>7</v>
       </c>
-      <c r="F189" s="6" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
+      <c r="G189" s="3" t="n">
         <v>3676</v>
       </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I189" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7530,12 @@
       </c>
     </row>
     <row r="193">
-      <c r="C193" s="2" t="inlineStr">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Alte actiuni economice</t>
         </is>
@@ -7314,7 +7546,11 @@
       <c r="E193" t="n">
         <v>7</v>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G193" s="3" t="n">
         <v>1200</v>
       </c>
@@ -7362,39 +7598,38 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="6" t="inlineStr">
+      <c r="A195" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B195" s="6" t="n"/>
-      <c r="C195" s="6" t="inlineStr">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D195" s="6" t="n">
+      <c r="D195" t="n">
         <v>245</v>
       </c>
-      <c r="E195" s="6" t="n">
+      <c r="E195" t="n">
         <v>7</v>
       </c>
-      <c r="F195" s="6" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
+      <c r="G195" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I195" s="6" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7656,12 @@
       </c>
     </row>
     <row r="197">
-      <c r="C197" s="2" t="inlineStr">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>96.02</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Partea a VII-a REZERVE, EXCEDENT/DEFICIT</t>
         </is>
@@ -7432,7 +7672,11 @@
       <c r="E197" t="n">
         <v>7</v>
       </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G197" s="3" t="n">
         <v>0</v>
       </c>
@@ -7443,7 +7687,12 @@
       </c>
     </row>
     <row r="198">
-      <c r="C198" s="2" t="inlineStr">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>97.02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
         <is>
           <t>REZERVE</t>
         </is>
@@ -7454,7 +7703,11 @@
       <c r="E198" t="n">
         <v>7</v>
       </c>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G198" s="3" t="n">
         <v>0</v>
       </c>
@@ -7465,7 +7718,12 @@
       </c>
     </row>
     <row r="199">
-      <c r="C199" s="2" t="inlineStr">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>98.02</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>EXCEDENT</t>
         </is>
@@ -7476,7 +7734,11 @@
       <c r="E199" t="n">
         <v>7</v>
       </c>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G199" s="3" t="n">
         <v>0</v>
       </c>
@@ -7487,7 +7749,12 @@
       </c>
     </row>
     <row r="200">
-      <c r="C200" s="2" t="inlineStr">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
@@ -7498,7 +7765,11 @@
       <c r="E200" t="n">
         <v>7</v>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
       <c r="G200" s="3" t="n">
         <v>25302.89</v>
       </c>
@@ -7536,7 +7807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7582,12 +7853,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7595,24 +7866,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7620,19 +7896,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7641,66 +7917,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>11.02 total: parent 35.729,00 != sum(children) 43.469,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>51.02 total: parent 20.766,72 != sum(children) 618,10 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7720,7 +8006,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7745,7 +8031,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7770,7 +8056,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7807,12 +8093,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -7820,12 +8106,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>65.02 total: parent 140.454,18 != sum(children) 4.509,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -7845,7 +8136,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7857,25 +8148,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>66.02 total: parent 4.138,50 != sum(children) 4,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7891,11 +8187,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7907,25 +8203,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>67.02 total: parent 41.100,99 != sum(children) 4.067,74 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7941,11 +8242,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7957,25 +8258,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>68.02 total: parent 35.360,00 != sum(children) 235,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8297,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -8007,25 +8313,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>70.02 total: parent 37.993,48 != sum(children) 10.111,20 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8041,11 +8352,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8057,25 +8368,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>74.02 total: parent 27.061,66 != sum(children) 8.241,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8091,11 +8407,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8107,25 +8423,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>84.02 total: parent 54.798,28 != sum(children) 21.256,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8141,11 +8462,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8166,1364 +8487,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>6</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>6</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>6</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>6</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>6</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>6</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>6</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>6</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>6</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>6</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>6</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>6</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>6</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>6</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>6</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>6</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>7</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>7</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>7</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>7</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>7</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>7</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>7</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>7</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>7</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>7</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>7</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>7</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>7</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
         <is>
           <t>duplicate of p3 with different values</t>
         </is>
@@ -9576,7 +8547,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -9586,7 +8557,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -9596,7 +8567,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.7</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="6">
@@ -9606,7 +8577,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +8587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">

--- a/data/2026/23-ialomita/92658-slobozia/budget_file.xlsx
+++ b/data/2026/23-ialomita/92658-slobozia/budget_file.xlsx
@@ -7807,7 +7807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7853,12 +7853,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7866,29 +7866,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7896,24 +7891,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7921,12 +7916,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>11.02 total: parent 35.729,00 != sum(children) 43.469,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7942,11 +7942,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7956,37 +7956,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.02 total: parent 35.729,00 != sum(children) 43.469,00 (1 children)</t>
+          <t>51.02 total: parent 20.766,72 != sum(children) 618,10 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.02 total: parent 20.766,72 != sum(children) 618,10 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8063,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8081,24 +8076,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>65.02 total: parent 140.454,18 != sum(children) 4.509,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8106,54 +8106,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.02 total: parent 140.454,18 != sum(children) 4.509,00 (2 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>66.02 total: parent 4.138,50 != sum(children) 4,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -8161,29 +8161,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>66.02 total: parent 4.138,50 != sum(children) 4,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -8191,24 +8186,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>67.02 total: parent 41.100,99 != sum(children) 4.067,74 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -8216,29 +8216,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.02 total: parent 41.100,99 != sum(children) 4.067,74 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -8246,24 +8241,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>68.02 total: parent 35.360,00 != sum(children) 235,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -8271,54 +8271,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68.02 total: parent 35.360,00 != sum(children) 235,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>70.02 total: parent 37.993,48 != sum(children) 10.111,20 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -8326,29 +8326,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.02 total: parent 37.993,48 != sum(children) 10.111,20 (2 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -8356,24 +8351,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>74.02 total: parent 27.061,66 != sum(children) 8.241,50 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -8381,29 +8381,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>74.02 total: parent 27.061,66 != sum(children) 8.241,50 (2 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -8411,42 +8406,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>84.02 total: parent 54.798,28 != sum(children) 21.256,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>84.02 total: parent 54.798,28 != sum(children) 21.256,00 (2 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -8470,31 +8465,6 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>duplicate of p3 with different values</t>
         </is>
@@ -8511,7 +8481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8533,7 +8503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8543,60 +8513,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>134</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>111</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2e9b92650eade08f3c5fee68</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dd864af7087a266099acd67afb6cdfc9fa4566fad0a1977217f337cf11235169</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL DETALIAT LA VENITURI SI CHELTUIELI PE CAPITOLE, SUBC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>unknown, pag. 1-7, 252 linii</t>
         </is>
